--- a/docs/ux/airbnb-pattern-analysis.xlsx
+++ b/docs/ux/airbnb-pattern-analysis.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="airbnb-desktop-grid" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="airbnb-desktop-data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="searchbar-dropdowns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="filtri-modale" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5658,4 +5660,1086 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb searchbar — i 3 dropdown (Dove/Date/Chi) misurati al click</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="56" t="inlineStr">
+        <is>
+          <t>Componente</t>
+        </is>
+      </c>
+      <c r="B3" s="56" t="inlineStr">
+        <is>
+          <t>Selettore / role</t>
+        </is>
+      </c>
+      <c r="C3" s="56" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E3" s="56" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="F3" s="56" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="G3" s="56" t="inlineStr">
+        <is>
+          <t>descrizione contenuto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>SEARCHBAR compatta</t>
+        </is>
+      </c>
+      <c r="B4" s="58" t="inlineStr">
+        <is>
+          <t>[data-testid=little-search]</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="n">
+        <v>543</v>
+      </c>
+      <c r="D4" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="59" t="n">
+        <v>439</v>
+      </c>
+      <c r="F4" s="59" t="n">
+        <v>46</v>
+      </c>
+      <c r="G4" s="58" t="inlineStr">
+        <is>
+          <t>"Milano: alloggi · 18-24 mag · Aggiungi ospiti" + lente rosa · pillola unica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ Filtri btn (separato)</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>button "Filtri"</t>
+        </is>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>999</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="59" t="n">
+        <v>83</v>
+      </c>
+      <c r="F5" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>separato dalla pillola searchbar · apre la modale full filtri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>SEARCHBAR espansa (3-seg)</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>(big-search)</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="n">
+        <v>320</v>
+      </c>
+      <c r="D6" s="59" t="n">
+        <v>95</v>
+      </c>
+      <c r="E6" s="59" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>al click campo: pillola si espande in 3 segmenti label-su / value-sotto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ segmento Dove</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>(button con label "Dove")</t>
+        </is>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>320</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <v>240</v>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>mostra "Milano, Lombardia" + ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ segmento Date</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>(button con label "Date")</t>
+        </is>
+      </c>
+      <c r="C8" s="59" t="n">
+        <v>580</v>
+      </c>
+      <c r="D8" s="59" t="n">
+        <v>95</v>
+      </c>
+      <c r="E8" s="59" t="n">
+        <v>240</v>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>mostra "18 mag - 24 mag" + ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ segmento Chi</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>(button con label "Chi")</t>
+        </is>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>840</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>95</v>
+      </c>
+      <c r="E9" s="59" t="n">
+        <v>240</v>
+      </c>
+      <c r="F9" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="58" t="inlineStr">
+        <is>
+          <t>mostra "4 ospiti, 2 neon..." + bottone Ricerca rosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ Ricerca CTA</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>button rosa #FF385C + lente</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D10" s="59" t="n">
+        <v>105</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="58" t="inlineStr">
+        <is>
+          <t>icona lente bianca su sfondo rosa · sempre visibile in modalità espansa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>DROPDOWN Dove</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>[role=listbox][aria-label=Suggerimenti di ricerca]</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>346</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>204</v>
+      </c>
+      <c r="E11" s="59" t="n">
+        <v>398</v>
+      </c>
+      <c r="F11" s="59" t="n">
+        <v>360</v>
+      </c>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>lista 5 suggerimenti località con icona pin · click → riempie input + chiude</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ suggerimento (riga)</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>(option role)</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="n">
+        <v>346</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <v>220</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>398</v>
+      </c>
+      <c r="F12" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="58" t="inlineStr">
+        <is>
+          <t>&lt;icon-pin&gt; + "Milano, Lombardia" · 5 voci default (storico+near)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>CALENDAR Date</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>[role=application][aria-label=Calendario]</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>343</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>264</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <v>829</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>359</v>
+      </c>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>calendario 2 mesi affiancati + toggle "Date/Flessibile" + footer check-in/out precision</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ toggle Date/Flessibile</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>(tabs)</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="n">
+        <v>575</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="59" t="n">
+        <v>440</v>
+      </c>
+      <c r="F14" s="59" t="n">
+        <v>56</v>
+      </c>
+      <c r="G14" s="58" t="inlineStr">
+        <is>
+          <t>"Date" (selected pillola bianca) + "Flessibile" — 2 modalità di scelta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ mese sx (Maggio)</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>(table)</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>360</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>264</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <v>380</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>280</v>
+      </c>
+      <c r="G15" s="58" t="inlineStr">
+        <is>
+          <t>griglia 7-col (L M M G V S D) · navigazione frecce sx/dx in alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ mese dx (Giugno)</t>
+        </is>
+      </c>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>(table)</t>
+        </is>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>760</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <v>264</v>
+      </c>
+      <c r="E16" s="59" t="n">
+        <v>380</v>
+      </c>
+      <c r="F16" s="59" t="n">
+        <v>280</v>
+      </c>
+      <c r="G16" s="58" t="inlineStr">
+        <is>
+          <t>stessa griglia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ check-in precision</t>
+        </is>
+      </c>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>(select dropdown)</t>
+        </is>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>470</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>600</v>
+      </c>
+      <c r="E17" s="59" t="n">
+        <v>250</v>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="58" t="inlineStr">
+        <is>
+          <t>"Check-in: Giorno esatto / ±1 / ±2 / ±3 / ±7 / ±14 giorni"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ check-out precision</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>(select dropdown)</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>720</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>600</v>
+      </c>
+      <c r="E18" s="59" t="n">
+        <v>250</v>
+      </c>
+      <c r="F18" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="58" t="inlineStr">
+        <is>
+          <t>stessa cosa per check-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>STEPPER Chi</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>(popup absolute)</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>750</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>180</v>
+      </c>
+      <c r="E19" s="59" t="n">
+        <v>400</v>
+      </c>
+      <c r="F19" s="59" t="n">
+        <v>380</v>
+      </c>
+      <c r="G19" s="58" t="inlineStr">
+        <is>
+          <t>lista 4 stepper ± con label+sublabel descrittivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ Adulti</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>(stepper row)</t>
+        </is>
+      </c>
+      <c r="C20" s="59" t="n">
+        <v>770</v>
+      </c>
+      <c r="D20" s="59" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>360</v>
+      </c>
+      <c r="F20" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" s="58" t="inlineStr">
+        <is>
+          <t>"Adulti" + sublabel "Da 13 in su" · stepper [- 2 +]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ Bambini</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>(stepper row)</t>
+        </is>
+      </c>
+      <c r="C21" s="59" t="n">
+        <v>770</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <v>270</v>
+      </c>
+      <c r="E21" s="59" t="n">
+        <v>360</v>
+      </c>
+      <c r="F21" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" s="58" t="inlineStr">
+        <is>
+          <t>"Bambini" + sublabel "Da 2 a 12 anni" · stepper [- 2 +]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ Neonati</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>(stepper row)</t>
+        </is>
+      </c>
+      <c r="C22" s="59" t="n">
+        <v>770</v>
+      </c>
+      <c r="D22" s="59" t="n">
+        <v>370</v>
+      </c>
+      <c r="E22" s="59" t="n">
+        <v>360</v>
+      </c>
+      <c r="F22" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" s="58" t="inlineStr">
+        <is>
+          <t>"Neonati" + sublabel "Fino a 2 anni" · stepper [- 2 +]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └ Animali domestici</t>
+        </is>
+      </c>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>(stepper row)</t>
+        </is>
+      </c>
+      <c r="C23" s="59" t="n">
+        <v>770</v>
+      </c>
+      <c r="D23" s="59" t="n">
+        <v>460</v>
+      </c>
+      <c r="E23" s="59" t="n">
+        <v>360</v>
+      </c>
+      <c r="F23" s="59" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" s="58" t="inlineStr">
+        <is>
+          <t>"Animali domestici" + link blu "Viaggi con animale di servizio?" · stepper [- 0 +]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb modale Filtri — sezioni gerarchiche (568×775 centrata x=487)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Dialogo modale aperto da bottone "Filtri" · 10 sezioni · scroll interno · footer fisso</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t>Sezione</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>Pattern UX</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>Contenuto</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Header modale</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>titolo + close X</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="inlineStr">
+        <is>
+          <t>"Filtri" centrato + close × top-right</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>sticky in alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>1. Consigliati per te</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>4 tile-card icona+label</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>🛏 "2+ camere" · 🧺 "Lavatrice" · 🍴 "Cucina" · 📅 "Cancellazione gratuita"</t>
+        </is>
+      </c>
+      <c r="D6" s="58" t="inlineStr">
+        <is>
+          <t>icone illustrate (non pittogrammi) · click toggle attivo · grid 4-col</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>2. Tipo di alloggio</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>segmented 3-radio</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>"Qualsiasi tipo" (selected) / "Stanza" / "Casa intera"</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>pillola unica con border attivo · pattern wizardstep1 nostro filter-chip</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>3. Fascia di prezzo</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>slider min-max + histogram + 2 input</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>slider 2-handle sopra histogram distribuzione prezzi (rosa Airbnb) · "Minimo €50" / "Massimo €2600+" sotto come input testuali editabili</t>
+        </is>
+      </c>
+      <c r="D8" s="58" t="inlineStr">
+        <is>
+          <t>⭐ pattern unico Airbnb · histogram aiuta scegliere min/max consapevolmente · UX premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>4. Stanze e letti</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>3 stepper ± con label "Qualsiasi"</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>Camere da letto [- Qualsiasi +] · Letti [- Qualsiasi +] · Bagni [- Qualsiasi +]</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>stepper riusa stesso pattern di "Chi/ospiti"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>5. Servizi</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>checkbox grid (mostra di più)</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="inlineStr">
+        <is>
+          <t>WiFi · Cucina · A/C · Lavatrice · Asciugatrice · Riscaldamento · TV · ...</t>
+        </is>
+      </c>
+      <c r="D10" s="58" t="inlineStr">
+        <is>
+          <t>inizialmente 8-10 visibili + "Mostra altro" expand · checkbox classici</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>6. Opzioni di prenotazione</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>4 chip toggle (con icona)</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>⚡ "Prenotazione immediata" · 🔑 "Self check-in" · 📅 "Cancellazione gratuita" · 🐾 "Animali ammessi"</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>chip pillola con icona linea + label · click toggle · grid 2x2 desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>7. Alloggi straordinari</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>2 tile-card grandi</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="inlineStr">
+        <is>
+          <t>"Amato dagli ospiti" (Gli alloggi più amati su Airbnb) · "Luxe" (Alloggi di lusso dal design favoloso)</t>
+        </is>
+      </c>
+      <c r="D12" s="58" t="inlineStr">
+        <is>
+          <t>tile più grandi delle "Consigliati" · 2-col · sublabel descrittivo · brand-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>8. Tipo di alloggio (accordion)</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>accordion ▼</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>Appartamento / Loft / Villa / Cottage / Stanza / B&amp;B / ...</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>collapsed default · expand mostra checkbox grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>9. Caratteristiche accessibilità</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>accordion ▼</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>Ingresso senza gradini · Bagno accessibile in sedia a rotelle · ...</t>
+        </is>
+      </c>
+      <c r="D14" s="58" t="inlineStr">
+        <is>
+          <t>collapsed default · WCAG-aware</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>10. Lingua dell'host</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>accordion ▼</t>
+        </is>
+      </c>
+      <c r="C15" s="58" t="inlineStr">
+        <is>
+          <t>Italiano / English / Deutsch / ...</t>
+        </is>
+      </c>
+      <c r="D15" s="58" t="inlineStr">
+        <is>
+          <t>collapsed default</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="57" t="inlineStr">
+        <is>
+          <t>Footer fisso</t>
+        </is>
+      </c>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>2 bottoni</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>"Cancella tutto" (sx, link blu)  +  "Mostra oltre 1.000 alloggi" (dx, primary rosa #FF385C)</t>
+        </is>
+      </c>
+      <c r="D16" s="58" t="inlineStr">
+        <is>
+          <t>⭐ il count si aggiorna LIVE mentre selezioni filtri (feedback immediato)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>PATTERN UX CHIAVE (Airbnb Filtri):</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>• Mai uniform-pattern: ogni sezione ha il pattern UX più adatto al tipo di filtro (slider per range, stepper per count, segmented per esclusivi, chip toggle per non-mutex, accordion per long lists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>• "Consigliati per te" in cima · personalizzato (più cliccati / più rilevanti per la query)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>• Histogram prezzo è SIGNATURE: aiuta capire dove sta la massa dei prezzi → scelta informata</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>• Footer LIVE count: "Mostra oltre 1.000 alloggi" si aggiorna ad ogni cambio · feedback immediato di rilevanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>• Accordion in fondo per filtri "long-tail" (tipo alloggio specifico, accessibilità, lingua) · evita modale infinita</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t>• Nessun click "Applica" intermedio · TUTTO live · solo "Cancella tutto" e "Mostra"</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>CONFRONTO CON wizardstep1 LIVINGAPPLE:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>• LivingApple: bottone Filtri + chip orizzontali sopra la lista · modale bottom-sheet mobile / centered desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t>• Airbnb: bottone Filtri solo · modale ricca · chip non in pagina (filtri appaiono solo in modale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>• LivingApple ha 5 macro-filtri (Sort, Mare, Piscina, Tipo, Camere) · Airbnb ne ha 10 · scopo diverso (booking vs platform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t>• Pattern Airbnb da adottare: histogram prezzo + LIVE count footer + tile-card "Consigliati"</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t>• Pattern LivingApple da MANTENERE: chip orizzontali above-fold per filtri primari (più veloce di aprire modale)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/ux/airbnb-pattern-analysis.xlsx
+++ b/docs/ux/airbnb-pattern-analysis.xlsx
@@ -11,6 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="airbnb-desktop-data" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="searchbar-dropdowns" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="filtri-modale" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="breakpoints" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="airbnb-mobile-grid" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="airbnb-mobile-data" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="airbnb-mobile-flow" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +66,25 @@
       <color rgb="00ffffff"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006b7280"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF385C"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +133,26 @@
         <bgColor rgb="00374151"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fef3c7"/>
+        <bgColor rgb="00fef3c7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009ca3af"/>
+        <bgColor rgb="009ca3af"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f9fafb"/>
+        <bgColor rgb="00f9fafb"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -289,11 +328,44 @@
         <color rgb="009ca3af"/>
       </right>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009ca3af"/>
+      </left>
+      <right style="thin">
+        <color rgb="009ca3af"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right/>
+      <top style="thin">
+        <color rgb="009ca3af"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="009ca3af"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009ca3af"/>
+      </left>
+      <right style="thin">
+        <color rgb="009ca3af"/>
+      </right>
+      <top style="thin">
+        <color rgb="009ca3af"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -377,6 +449,43 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,7 +977,7 @@
     <row r="2" ht="15" customHeight="1"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>Header sticky  1526×96  (z-index 10)</t>
         </is>
@@ -1796,13 +1905,13 @@
       <c r="DD16" s="11" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>CARD listing  [itemprop=itemListElement]</t>
         </is>
       </c>
       <c r="AA17" s="14" t="n"/>
-      <c r="AC17" s="31" t="inlineStr">
+      <c r="AC17" s="61" t="inlineStr">
         <is>
           <t>CARD listing #2</t>
         </is>
@@ -2882,7 +2991,7 @@
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="D40" s="48" t="n"/>
-      <c r="E40" s="49" t="inlineStr">
+      <c r="E40" s="62" t="inlineStr">
         <is>
           <t>983 € 532 € in totale  (prezzo: vecchio strike + nuovo)</t>
         </is>
@@ -2910,7 +3019,7 @@
       <c r="Z40" s="16" t="n"/>
       <c r="AA40" s="50" t="n"/>
       <c r="AC40" s="48" t="n"/>
-      <c r="AD40" s="49" t="inlineStr">
+      <c r="AD40" s="62" t="inlineStr">
         <is>
           <t>524 € 430 € in totale · Cancellazione gratuita</t>
         </is>
@@ -3015,13 +3124,13 @@
       <c r="DD43" s="14" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="D44" s="31" t="inlineStr">
+      <c r="D44" s="61" t="inlineStr">
         <is>
           <t>CARD #3</t>
         </is>
       </c>
       <c r="AA44" s="14" t="n"/>
-      <c r="AC44" s="31" t="inlineStr">
+      <c r="AC44" s="61" t="inlineStr">
         <is>
           <t>CARD #4</t>
         </is>
@@ -6742,4 +6851,3377 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb — 11 breakpoint misurati via Chrome MCP (DevTools Responsive + iPhone 14 Pro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="56" t="inlineStr">
+        <is>
+          <t>Width (px)</t>
+        </is>
+      </c>
+      <c r="B3" s="56" t="inlineStr">
+        <is>
+          <t>Map state</t>
+        </is>
+      </c>
+      <c r="C3" s="56" t="inlineStr">
+        <is>
+          <t>List grid</t>
+        </is>
+      </c>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>Header pattern</t>
+        </is>
+      </c>
+      <c r="E3" s="56" t="inlineStr">
+        <is>
+          <t>Searchbar w</t>
+        </is>
+      </c>
+      <c r="F3" s="56" t="inlineStr">
+        <is>
+          <t>Filter btn</t>
+        </is>
+      </c>
+      <c r="G3" s="56" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B4" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 1125w</t>
+        </is>
+      </c>
+      <c r="C4" s="58" t="inlineStr">
+        <is>
+          <t>3 cards/riga (359w)</t>
+        </is>
+      </c>
+      <c r="D4" s="58" t="inlineStr">
+        <is>
+          <t>searchbar centrata 388×46</t>
+        </is>
+      </c>
+      <c r="E4" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F4" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G4" s="58" t="inlineStr">
+        <is>
+          <t>Layout XL ultrawide · listCol 1124</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 885w</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (426w)</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>searchbar centrata 388×46</t>
+        </is>
+      </c>
+      <c r="E5" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F5" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>Layout L · listCol 876</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="63" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 700w</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (329w)</t>
+        </is>
+      </c>
+      <c r="D6" s="58" t="inlineStr">
+        <is>
+          <t>searchbar centrata 388×46</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F6" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>Desktop standard (riferimento)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="63" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 650w</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (303w)</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>searchbar centrata 388×46</t>
+        </is>
+      </c>
+      <c r="E7" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>Laptop standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="63" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 433w</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (332w)</t>
+        </is>
+      </c>
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>searchbar INLINE LEFT (vicino logo)</t>
+        </is>
+      </c>
+      <c r="E8" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G8" s="64" t="inlineStr">
+        <is>
+          <t>🎯 Header layout change (centrata→inline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 473w</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>1 card/riga (440w)</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>searchbar inline-left</t>
+        </is>
+      </c>
+      <c r="E9" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F9" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G9" s="64" t="inlineStr">
+        <is>
+          <t>🎯 Card grid 2→1 col (in modo desktop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="63" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>visible dx 399w</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="inlineStr">
+        <is>
+          <t>1 card/riga (440w)</t>
+        </is>
+      </c>
+      <c r="D10" s="58" t="inlineStr">
+        <is>
+          <t>searchbar inline-left</t>
+        </is>
+      </c>
+      <c r="E10" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F10" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G10" s="58" t="inlineStr">
+        <is>
+          <t>Mostra mappa btn pre-cooked nel DOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>HIDDEN + floating btn "Mostra la mappa" (173×48 bottom-center)</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (349w)</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>searchbar inline-left</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F11" s="59" t="inlineStr">
+        <is>
+          <t>83×40</t>
+        </is>
+      </c>
+      <c r="G11" s="64" t="inlineStr">
+        <is>
+          <t>🎯 Map breakpoint (mappa sparisce, lista riempie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>FULL-WIDTH TOP + drag handle linea grigia centrata</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (328w)</t>
+        </is>
+      </c>
+      <c r="D12" s="64" t="inlineStr">
+        <is>
+          <t>searchbar PILLOLA mobile + back arrow + filtri icon</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="inlineStr">
+        <is>
+          <t>no little-search</t>
+        </is>
+      </c>
+      <c r="F12" s="59" t="inlineStr">
+        <is>
+          <t>icon 40×40</t>
+        </is>
+      </c>
+      <c r="G12" s="64" t="inlineStr">
+        <is>
+          <t>🎯 Mobile mode (bottom nav: Esplora·Preferiti·Viaggi·Messaggi·Profilo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>full-width top</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>2 cards/riga (257w)</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>searchbar pillola mobile</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="inlineStr">
+        <is>
+          <t>no little-search</t>
+        </is>
+      </c>
+      <c r="F13" s="59" t="inlineStr">
+        <is>
+          <t>icon 40×40</t>
+        </is>
+      </c>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>Mobile mid-range</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>full-width top (363×819 con UA iPhone)</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>1 card/riga (315w)</t>
+        </is>
+      </c>
+      <c r="D14" s="58" t="inlineStr">
+        <is>
+          <t>searchbar pillola "Milano: alloggi" + ← back + ≡ filtri</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="inlineStr">
+        <is>
+          <t>no little-search</t>
+        </is>
+      </c>
+      <c r="F14" s="59" t="inlineStr">
+        <is>
+          <t>icon 40×40</t>
+        </is>
+      </c>
+      <c r="G14" s="64" t="inlineStr">
+        <is>
+          <t>🎯 Card grid 2→1 mobile (iPhone 14 Pro UA mobile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>BREAKPOINT CRITICI IDENTIFICATI:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>• ~2200 px : 3→2 cards/riga (in modalità desktop XL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>• ~1440 px : searchbar centrata → inline-left (header layout change)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>• ~1100 px : 2→1 card/riga (modalità desktop con sidebar mappa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>• ~870 px : mappa scompare → "Mostra mappa" floating btn appare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>• ~770 px : layout desktop → mobile completo (mappa torna full-top, drag handle, pillola searchbar, bottom nav)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>• ~480 px : in mobile, 2→1 card/riga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>CONFRONTO con LivingApple wizardstep1 (CSS audit):</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>• Airbnb usa 6 breakpoint visibili, LivingApple ne ha 3 (`--bp-sm 640 / --bp-md 768 / --bp-lg 1024`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>• Airbnb sezionalizza in 4 zone: ultrawide (&gt;2200), desktop (1100-2200), tablet (770-1100), mobile (&lt;770)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>• LivingApple ha solo desktop (≥768) vs mobile (&lt;768) — molto più semplificato</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t>• Per redesign wizardstep1: aggiungere breakpoint intermedio ~1100 per cambiare grid sidebar BookingSidebar?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" min="11" max="11"/>
+    <col width="2" customWidth="1" min="12" max="12"/>
+    <col width="2" customWidth="1" min="13" max="13"/>
+    <col width="2" customWidth="1" min="14" max="14"/>
+    <col width="2" customWidth="1" min="15" max="15"/>
+    <col width="2" customWidth="1" min="16" max="16"/>
+    <col width="2" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="2" customWidth="1" min="19" max="19"/>
+    <col width="2" customWidth="1" min="20" max="20"/>
+    <col width="2" customWidth="1" min="21" max="21"/>
+    <col width="2" customWidth="1" min="22" max="22"/>
+    <col width="2" customWidth="1" min="23" max="23"/>
+    <col width="2" customWidth="1" min="24" max="24"/>
+    <col width="2" customWidth="1" min="25" max="25"/>
+    <col width="2" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="2" customWidth="1" min="28" max="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb iPhone 14 Pro (378×819, UA mobile, DPR 1.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>←</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="28" t="n"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Milano: alloggi
+18-24 mag · 4 ospiti</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="4" t="n"/>
+      <c r="V3" s="4" t="n"/>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="11" t="n"/>
+      <c r="Z3" s="28" t="n"/>
+      <c r="AA3" s="10" t="inlineStr">
+        <is>
+          <t>≡</t>
+        </is>
+      </c>
+      <c r="AB3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="13" t="n"/>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+      <c r="Z4" s="53" t="n"/>
+      <c r="AA4" s="13" t="n"/>
+      <c r="AB4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="16" t="n"/>
+      <c r="W5" s="16" t="n"/>
+      <c r="X5" s="16" t="n"/>
+      <c r="Y5" s="17" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="15" t="n"/>
+      <c r="AB5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>header pillola 40×40 sx (back) + 211×58 centro (searchbar) + 40×40 dx (filtri)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1"/>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>[ MAPPA Google Maps full-width ]
+363 × 788 px
+Price markers (760€ · 891€ · 1.402€ · 1.036€ · 1.035€ · 859€ · 813€ · ecc.)
+📍 Milano centro pin
+2 km scale</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4" t="n"/>
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="4" t="n"/>
+      <c r="X8" s="4" t="n"/>
+      <c r="Y8" s="4" t="n"/>
+      <c r="Z8" s="4" t="n"/>
+      <c r="AA8" s="4" t="n"/>
+      <c r="AB8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="13" t="n"/>
+      <c r="AB9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="13" t="n"/>
+      <c r="AB10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="AB11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="13" t="n"/>
+      <c r="AB12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="13" t="n"/>
+      <c r="AB13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="13" t="n"/>
+      <c r="AB14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="AB15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="13" t="n"/>
+      <c r="AB16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="AB17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="13" t="n"/>
+      <c r="AB18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="AB19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="13" t="n"/>
+      <c r="AB20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="13" t="n"/>
+      <c r="AB21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="13" t="n"/>
+      <c r="AB22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="13" t="n"/>
+      <c r="AB23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="13" t="n"/>
+      <c r="AB24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="13" t="n"/>
+      <c r="AB25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="AB26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="13" t="n"/>
+      <c r="AB27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="13" t="n"/>
+      <c r="AB28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="13" t="n"/>
+      <c r="AB29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="16" t="n"/>
+      <c r="R30" s="16" t="n"/>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="16" t="n"/>
+      <c r="V30" s="16" t="n"/>
+      <c r="W30" s="16" t="n"/>
+      <c r="X30" s="16" t="n"/>
+      <c r="Y30" s="16" t="n"/>
+      <c r="Z30" s="16" t="n"/>
+      <c r="AA30" s="16" t="n"/>
+      <c r="AB30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="L31" s="65" t="inlineStr">
+        <is>
+          <t>═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="52" t="inlineStr">
+        <is>
+          <t>↕ DRAG HANDLE (linea grigia centrata · 157×0px coord, visibile come pill 30×4 pattern bottom-sheet) ↕</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="27" t="n"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="n"/>
+      <c r="O33" s="28" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n"/>
+      <c r="R33" s="28" t="n"/>
+      <c r="S33" s="28" t="n"/>
+      <c r="T33" s="28" t="n"/>
+      <c r="U33" s="28" t="n"/>
+      <c r="V33" s="28" t="n"/>
+      <c r="W33" s="28" t="n"/>
+      <c r="X33" s="28" t="n"/>
+      <c r="Y33" s="28" t="n"/>
+      <c r="Z33" s="28" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="29" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>DRAWER (pull-up bottom-sheet · default peek-bottom)</t>
+        </is>
+      </c>
+      <c r="AB34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="66" t="inlineStr">
+        <is>
+          <t>Oltre 1.000 alloggi  (h1)</t>
+        </is>
+      </c>
+      <c r="AB35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>Come ordiniamo i risultati ⓘ</t>
+        </is>
+      </c>
+      <c r="AB36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="32" t="n"/>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="53" t="n"/>
+      <c r="G37" s="53" t="n"/>
+      <c r="H37" s="53" t="n"/>
+      <c r="I37" s="53" t="n"/>
+      <c r="J37" s="53" t="n"/>
+      <c r="K37" s="53" t="n"/>
+      <c r="L37" s="53" t="n"/>
+      <c r="M37" s="53" t="n"/>
+      <c r="N37" s="53" t="n"/>
+      <c r="O37" s="53" t="n"/>
+      <c r="P37" s="53" t="n"/>
+      <c r="Q37" s="53" t="n"/>
+      <c r="R37" s="53" t="n"/>
+      <c r="S37" s="53" t="n"/>
+      <c r="T37" s="53" t="n"/>
+      <c r="U37" s="53" t="n"/>
+      <c r="V37" s="53" t="n"/>
+      <c r="W37" s="53" t="n"/>
+      <c r="X37" s="53" t="n"/>
+      <c r="Y37" s="53" t="n"/>
+      <c r="Z37" s="53" t="n"/>
+      <c r="AA37" s="53" t="n"/>
+      <c r="AB37" s="37" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="32" t="n"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="28" t="n"/>
+      <c r="J38" s="28" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="28" t="n"/>
+      <c r="M38" s="28" t="n"/>
+      <c r="N38" s="28" t="n"/>
+      <c r="O38" s="28" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n"/>
+      <c r="R38" s="28" t="n"/>
+      <c r="S38" s="28" t="n"/>
+      <c r="T38" s="28" t="n"/>
+      <c r="U38" s="28" t="n"/>
+      <c r="V38" s="28" t="n"/>
+      <c r="W38" s="28" t="n"/>
+      <c r="X38" s="28" t="n"/>
+      <c r="Y38" s="28" t="n"/>
+      <c r="Z38" s="28" t="n"/>
+      <c r="AA38" s="29" t="n"/>
+      <c r="AB38" s="37" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="32" t="n"/>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>CARD listing (315×451 px · 1 per riga)</t>
+        </is>
+      </c>
+      <c r="AA39" s="14" t="n"/>
+      <c r="AB39" s="37" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="32" t="n"/>
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="34" t="n"/>
+      <c r="E40" s="34" t="n"/>
+      <c r="F40" s="34" t="n"/>
+      <c r="G40" s="34" t="n"/>
+      <c r="H40" s="34" t="n"/>
+      <c r="I40" s="34" t="n"/>
+      <c r="J40" s="34" t="n"/>
+      <c r="K40" s="34" t="n"/>
+      <c r="L40" s="34" t="n"/>
+      <c r="M40" s="34" t="n"/>
+      <c r="N40" s="34" t="n"/>
+      <c r="O40" s="34" t="n"/>
+      <c r="P40" s="34" t="n"/>
+      <c r="Q40" s="34" t="n"/>
+      <c r="R40" s="34" t="n"/>
+      <c r="S40" s="34" t="n"/>
+      <c r="T40" s="34" t="n"/>
+      <c r="U40" s="34" t="n"/>
+      <c r="V40" s="34" t="n"/>
+      <c r="W40" s="34" t="n"/>
+      <c r="X40" s="35" t="inlineStr">
+        <is>
+          <t>♡</t>
+        </is>
+      </c>
+      <c r="Y40" s="34" t="n"/>
+      <c r="Z40" s="36" t="n"/>
+      <c r="AA40" s="37" t="n"/>
+      <c r="AB40" s="37" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="32" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="39" t="n"/>
+      <c r="I41" s="39" t="n"/>
+      <c r="J41" s="39" t="n"/>
+      <c r="K41" s="39" t="n"/>
+      <c r="L41" s="39" t="n"/>
+      <c r="M41" s="39" t="n"/>
+      <c r="N41" s="39" t="n"/>
+      <c r="O41" s="39" t="n"/>
+      <c r="P41" s="39" t="n"/>
+      <c r="Q41" s="39" t="n"/>
+      <c r="R41" s="39" t="n"/>
+      <c r="S41" s="39" t="n"/>
+      <c r="T41" s="39" t="n"/>
+      <c r="U41" s="39" t="n"/>
+      <c r="V41" s="39" t="n"/>
+      <c r="W41" s="39" t="n"/>
+      <c r="X41" s="39" t="n"/>
+      <c r="Y41" s="39" t="n"/>
+      <c r="Z41" s="40" t="n"/>
+      <c r="AA41" s="37" t="n"/>
+      <c r="AB41" s="37" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="32" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="39" t="n"/>
+      <c r="H42" s="39" t="n"/>
+      <c r="I42" s="39" t="n"/>
+      <c r="J42" s="39" t="n"/>
+      <c r="K42" s="39" t="n"/>
+      <c r="L42" s="39" t="n"/>
+      <c r="M42" s="39" t="n"/>
+      <c r="N42" s="39" t="n"/>
+      <c r="O42" s="39" t="n"/>
+      <c r="P42" s="39" t="n"/>
+      <c r="Q42" s="39" t="n"/>
+      <c r="R42" s="39" t="n"/>
+      <c r="S42" s="39" t="n"/>
+      <c r="T42" s="39" t="n"/>
+      <c r="U42" s="39" t="n"/>
+      <c r="V42" s="39" t="n"/>
+      <c r="W42" s="39" t="n"/>
+      <c r="X42" s="39" t="n"/>
+      <c r="Y42" s="39" t="n"/>
+      <c r="Z42" s="40" t="n"/>
+      <c r="AA42" s="37" t="n"/>
+      <c r="AB42" s="37" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="39" t="n"/>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="39" t="n"/>
+      <c r="L43" s="39" t="n"/>
+      <c r="M43" s="39" t="n"/>
+      <c r="N43" s="39" t="n"/>
+      <c r="O43" s="39" t="n"/>
+      <c r="P43" s="39" t="n"/>
+      <c r="Q43" s="39" t="n"/>
+      <c r="R43" s="39" t="n"/>
+      <c r="S43" s="39" t="n"/>
+      <c r="T43" s="39" t="n"/>
+      <c r="U43" s="39" t="n"/>
+      <c r="V43" s="39" t="n"/>
+      <c r="W43" s="39" t="n"/>
+      <c r="X43" s="39" t="n"/>
+      <c r="Y43" s="39" t="n"/>
+      <c r="Z43" s="40" t="n"/>
+      <c r="AA43" s="37" t="n"/>
+      <c r="AB43" s="37" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="32" t="n"/>
+      <c r="B44" s="32" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="39" t="n"/>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="39" t="n"/>
+      <c r="L44" s="39" t="n"/>
+      <c r="M44" s="39" t="n"/>
+      <c r="N44" s="39" t="n"/>
+      <c r="O44" s="39" t="n"/>
+      <c r="P44" s="39" t="n"/>
+      <c r="Q44" s="39" t="n"/>
+      <c r="R44" s="39" t="n"/>
+      <c r="S44" s="39" t="n"/>
+      <c r="T44" s="39" t="n"/>
+      <c r="U44" s="39" t="n"/>
+      <c r="V44" s="39" t="n"/>
+      <c r="W44" s="39" t="n"/>
+      <c r="X44" s="39" t="n"/>
+      <c r="Y44" s="39" t="n"/>
+      <c r="Z44" s="40" t="n"/>
+      <c r="AA44" s="37" t="n"/>
+      <c r="AB44" s="37" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="32" t="n"/>
+      <c r="B45" s="32" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="39" t="n"/>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="39" t="n"/>
+      <c r="K45" s="39" t="n"/>
+      <c r="L45" s="39" t="n"/>
+      <c r="M45" s="39" t="n"/>
+      <c r="N45" s="39" t="n"/>
+      <c r="O45" s="39" t="n"/>
+      <c r="P45" s="39" t="n"/>
+      <c r="Q45" s="39" t="n"/>
+      <c r="R45" s="39" t="n"/>
+      <c r="S45" s="39" t="n"/>
+      <c r="T45" s="39" t="n"/>
+      <c r="U45" s="39" t="n"/>
+      <c r="V45" s="39" t="n"/>
+      <c r="W45" s="39" t="n"/>
+      <c r="X45" s="39" t="n"/>
+      <c r="Y45" s="39" t="n"/>
+      <c r="Z45" s="40" t="n"/>
+      <c r="AA45" s="37" t="n"/>
+      <c r="AB45" s="37" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="32" t="n"/>
+      <c r="B46" s="32" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="39" t="n"/>
+      <c r="F46" s="39" t="n"/>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="39" t="n"/>
+      <c r="I46" s="39" t="n"/>
+      <c r="J46" s="39" t="n"/>
+      <c r="K46" s="39" t="n"/>
+      <c r="L46" s="39" t="n"/>
+      <c r="M46" s="39" t="n"/>
+      <c r="N46" s="39" t="n"/>
+      <c r="O46" s="39" t="n"/>
+      <c r="P46" s="39" t="n"/>
+      <c r="Q46" s="39" t="n"/>
+      <c r="R46" s="39" t="n"/>
+      <c r="S46" s="39" t="n"/>
+      <c r="T46" s="39" t="n"/>
+      <c r="U46" s="39" t="n"/>
+      <c r="V46" s="39" t="n"/>
+      <c r="W46" s="39" t="n"/>
+      <c r="X46" s="39" t="n"/>
+      <c r="Y46" s="39" t="n"/>
+      <c r="Z46" s="40" t="n"/>
+      <c r="AA46" s="37" t="n"/>
+      <c r="AB46" s="37" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="32" t="n"/>
+      <c r="B47" s="32" t="n"/>
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="39" t="n"/>
+      <c r="E47" s="39" t="n"/>
+      <c r="F47" s="39" t="n"/>
+      <c r="G47" s="39" t="n"/>
+      <c r="H47" s="39" t="n"/>
+      <c r="I47" s="39" t="n"/>
+      <c r="J47" s="39" t="n"/>
+      <c r="K47" s="39" t="n"/>
+      <c r="L47" s="39" t="n"/>
+      <c r="M47" s="39" t="n"/>
+      <c r="N47" s="39" t="n"/>
+      <c r="O47" s="39" t="n"/>
+      <c r="P47" s="39" t="n"/>
+      <c r="Q47" s="39" t="n"/>
+      <c r="R47" s="39" t="n"/>
+      <c r="S47" s="39" t="n"/>
+      <c r="T47" s="39" t="n"/>
+      <c r="U47" s="39" t="n"/>
+      <c r="V47" s="39" t="n"/>
+      <c r="W47" s="39" t="n"/>
+      <c r="X47" s="39" t="n"/>
+      <c r="Y47" s="39" t="n"/>
+      <c r="Z47" s="40" t="n"/>
+      <c r="AA47" s="37" t="n"/>
+      <c r="AB47" s="37" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="32" t="n"/>
+      <c r="B48" s="32" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="39" t="n"/>
+      <c r="F48" s="39" t="n"/>
+      <c r="G48" s="39" t="n"/>
+      <c r="H48" s="39" t="n"/>
+      <c r="I48" s="39" t="n"/>
+      <c r="J48" s="39" t="n"/>
+      <c r="K48" s="39" t="n"/>
+      <c r="L48" s="41" t="inlineStr">
+        <is>
+          <t>[ FOTO 315×395 ]</t>
+        </is>
+      </c>
+      <c r="R48" s="39" t="n"/>
+      <c r="S48" s="39" t="n"/>
+      <c r="T48" s="39" t="n"/>
+      <c r="U48" s="39" t="n"/>
+      <c r="V48" s="39" t="n"/>
+      <c r="W48" s="39" t="n"/>
+      <c r="X48" s="39" t="n"/>
+      <c r="Y48" s="39" t="n"/>
+      <c r="Z48" s="40" t="n"/>
+      <c r="AA48" s="37" t="n"/>
+      <c r="AB48" s="37" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="32" t="n"/>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="38" t="n"/>
+      <c r="D49" s="39" t="n"/>
+      <c r="E49" s="39" t="n"/>
+      <c r="F49" s="39" t="n"/>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="39" t="n"/>
+      <c r="I49" s="39" t="n"/>
+      <c r="J49" s="39" t="n"/>
+      <c r="K49" s="39" t="n"/>
+      <c r="L49" s="39" t="n"/>
+      <c r="M49" s="39" t="n"/>
+      <c r="N49" s="39" t="n"/>
+      <c r="O49" s="39" t="n"/>
+      <c r="P49" s="39" t="n"/>
+      <c r="Q49" s="39" t="n"/>
+      <c r="R49" s="39" t="n"/>
+      <c r="S49" s="39" t="n"/>
+      <c r="T49" s="39" t="n"/>
+      <c r="U49" s="39" t="n"/>
+      <c r="V49" s="39" t="n"/>
+      <c r="W49" s="39" t="n"/>
+      <c r="X49" s="39" t="n"/>
+      <c r="Y49" s="39" t="n"/>
+      <c r="Z49" s="40" t="n"/>
+      <c r="AA49" s="37" t="n"/>
+      <c r="AB49" s="37" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="32" t="n"/>
+      <c r="B50" s="32" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="39" t="n"/>
+      <c r="F50" s="39" t="n"/>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="39" t="n"/>
+      <c r="I50" s="39" t="n"/>
+      <c r="J50" s="39" t="n"/>
+      <c r="K50" s="39" t="n"/>
+      <c r="L50" s="39" t="n"/>
+      <c r="M50" s="39" t="n"/>
+      <c r="N50" s="39" t="n"/>
+      <c r="O50" s="39" t="n"/>
+      <c r="P50" s="39" t="n"/>
+      <c r="Q50" s="39" t="n"/>
+      <c r="R50" s="39" t="n"/>
+      <c r="S50" s="39" t="n"/>
+      <c r="T50" s="39" t="n"/>
+      <c r="U50" s="39" t="n"/>
+      <c r="V50" s="39" t="n"/>
+      <c r="W50" s="39" t="n"/>
+      <c r="X50" s="39" t="n"/>
+      <c r="Y50" s="39" t="n"/>
+      <c r="Z50" s="40" t="n"/>
+      <c r="AA50" s="37" t="n"/>
+      <c r="AB50" s="37" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="32" t="n"/>
+      <c r="B51" s="32" t="n"/>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="39" t="n"/>
+      <c r="E51" s="39" t="n"/>
+      <c r="F51" s="39" t="n"/>
+      <c r="G51" s="39" t="n"/>
+      <c r="H51" s="39" t="n"/>
+      <c r="I51" s="39" t="n"/>
+      <c r="J51" s="39" t="n"/>
+      <c r="K51" s="39" t="n"/>
+      <c r="L51" s="39" t="n"/>
+      <c r="M51" s="39" t="n"/>
+      <c r="N51" s="39" t="n"/>
+      <c r="O51" s="39" t="n"/>
+      <c r="P51" s="39" t="n"/>
+      <c r="Q51" s="39" t="n"/>
+      <c r="R51" s="39" t="n"/>
+      <c r="S51" s="39" t="n"/>
+      <c r="T51" s="39" t="n"/>
+      <c r="U51" s="39" t="n"/>
+      <c r="V51" s="39" t="n"/>
+      <c r="W51" s="39" t="n"/>
+      <c r="X51" s="39" t="n"/>
+      <c r="Y51" s="39" t="n"/>
+      <c r="Z51" s="40" t="n"/>
+      <c r="AA51" s="37" t="n"/>
+      <c r="AB51" s="37" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="32" t="n"/>
+      <c r="B52" s="32" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="39" t="n"/>
+      <c r="F52" s="39" t="n"/>
+      <c r="G52" s="39" t="n"/>
+      <c r="H52" s="39" t="n"/>
+      <c r="I52" s="39" t="n"/>
+      <c r="J52" s="39" t="n"/>
+      <c r="K52" s="39" t="n"/>
+      <c r="L52" s="39" t="n"/>
+      <c r="M52" s="39" t="n"/>
+      <c r="N52" s="39" t="n"/>
+      <c r="O52" s="39" t="n"/>
+      <c r="P52" s="39" t="n"/>
+      <c r="Q52" s="39" t="n"/>
+      <c r="R52" s="39" t="n"/>
+      <c r="S52" s="39" t="n"/>
+      <c r="T52" s="39" t="n"/>
+      <c r="U52" s="39" t="n"/>
+      <c r="V52" s="39" t="n"/>
+      <c r="W52" s="39" t="n"/>
+      <c r="X52" s="39" t="n"/>
+      <c r="Y52" s="39" t="n"/>
+      <c r="Z52" s="40" t="n"/>
+      <c r="AA52" s="37" t="n"/>
+      <c r="AB52" s="37" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="32" t="n"/>
+      <c r="B53" s="32" t="n"/>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="39" t="n"/>
+      <c r="I53" s="39" t="n"/>
+      <c r="J53" s="39" t="n"/>
+      <c r="K53" s="39" t="n"/>
+      <c r="L53" s="39" t="n"/>
+      <c r="M53" s="39" t="n"/>
+      <c r="N53" s="39" t="n"/>
+      <c r="O53" s="39" t="n"/>
+      <c r="P53" s="39" t="n"/>
+      <c r="Q53" s="39" t="n"/>
+      <c r="R53" s="39" t="n"/>
+      <c r="S53" s="39" t="n"/>
+      <c r="T53" s="39" t="n"/>
+      <c r="U53" s="39" t="n"/>
+      <c r="V53" s="39" t="n"/>
+      <c r="W53" s="39" t="n"/>
+      <c r="X53" s="39" t="n"/>
+      <c r="Y53" s="39" t="n"/>
+      <c r="Z53" s="40" t="n"/>
+      <c r="AA53" s="37" t="n"/>
+      <c r="AB53" s="37" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="32" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="39" t="n"/>
+      <c r="F54" s="39" t="n"/>
+      <c r="G54" s="39" t="n"/>
+      <c r="H54" s="39" t="n"/>
+      <c r="I54" s="39" t="n"/>
+      <c r="J54" s="39" t="n"/>
+      <c r="K54" s="39" t="n"/>
+      <c r="L54" s="39" t="n"/>
+      <c r="M54" s="39" t="n"/>
+      <c r="N54" s="39" t="n"/>
+      <c r="O54" s="39" t="n"/>
+      <c r="P54" s="39" t="n"/>
+      <c r="Q54" s="39" t="n"/>
+      <c r="R54" s="39" t="n"/>
+      <c r="S54" s="39" t="n"/>
+      <c r="T54" s="39" t="n"/>
+      <c r="U54" s="39" t="n"/>
+      <c r="V54" s="39" t="n"/>
+      <c r="W54" s="39" t="n"/>
+      <c r="X54" s="39" t="n"/>
+      <c r="Y54" s="39" t="n"/>
+      <c r="Z54" s="40" t="n"/>
+      <c r="AA54" s="37" t="n"/>
+      <c r="AB54" s="37" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="32" t="n"/>
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="39" t="n"/>
+      <c r="G55" s="39" t="n"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="n"/>
+      <c r="J55" s="39" t="n"/>
+      <c r="K55" s="39" t="n"/>
+      <c r="L55" s="39" t="n"/>
+      <c r="M55" s="39" t="n"/>
+      <c r="N55" s="39" t="n"/>
+      <c r="O55" s="39" t="n"/>
+      <c r="P55" s="39" t="n"/>
+      <c r="Q55" s="39" t="n"/>
+      <c r="R55" s="39" t="n"/>
+      <c r="S55" s="39" t="n"/>
+      <c r="T55" s="39" t="n"/>
+      <c r="U55" s="39" t="n"/>
+      <c r="V55" s="39" t="n"/>
+      <c r="W55" s="39" t="n"/>
+      <c r="X55" s="39" t="n"/>
+      <c r="Y55" s="39" t="n"/>
+      <c r="Z55" s="40" t="n"/>
+      <c r="AA55" s="37" t="n"/>
+      <c r="AB55" s="37" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="32" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="39" t="n"/>
+      <c r="F56" s="39" t="n"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="39" t="n"/>
+      <c r="I56" s="39" t="n"/>
+      <c r="J56" s="39" t="n"/>
+      <c r="K56" s="39" t="n"/>
+      <c r="L56" s="39" t="n"/>
+      <c r="M56" s="39" t="n"/>
+      <c r="N56" s="39" t="n"/>
+      <c r="O56" s="39" t="n"/>
+      <c r="P56" s="39" t="n"/>
+      <c r="Q56" s="39" t="n"/>
+      <c r="R56" s="39" t="n"/>
+      <c r="S56" s="39" t="n"/>
+      <c r="T56" s="39" t="n"/>
+      <c r="U56" s="39" t="n"/>
+      <c r="V56" s="39" t="n"/>
+      <c r="W56" s="39" t="n"/>
+      <c r="X56" s="39" t="n"/>
+      <c r="Y56" s="39" t="n"/>
+      <c r="Z56" s="40" t="n"/>
+      <c r="AA56" s="37" t="n"/>
+      <c r="AB56" s="37" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="32" t="n"/>
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="38" t="n"/>
+      <c r="D57" s="39" t="n"/>
+      <c r="E57" s="39" t="n"/>
+      <c r="F57" s="39" t="n"/>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="39" t="n"/>
+      <c r="I57" s="39" t="n"/>
+      <c r="J57" s="39" t="n"/>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="39" t="n"/>
+      <c r="M57" s="39" t="n"/>
+      <c r="N57" s="39" t="n"/>
+      <c r="O57" s="39" t="n"/>
+      <c r="P57" s="39" t="n"/>
+      <c r="Q57" s="39" t="n"/>
+      <c r="R57" s="39" t="n"/>
+      <c r="S57" s="39" t="n"/>
+      <c r="T57" s="39" t="n"/>
+      <c r="U57" s="39" t="n"/>
+      <c r="V57" s="39" t="n"/>
+      <c r="W57" s="39" t="n"/>
+      <c r="X57" s="39" t="n"/>
+      <c r="Y57" s="39" t="n"/>
+      <c r="Z57" s="40" t="n"/>
+      <c r="AA57" s="37" t="n"/>
+      <c r="AB57" s="37" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="32" t="n"/>
+      <c r="B58" s="32" t="n"/>
+      <c r="C58" s="42" t="n"/>
+      <c r="D58" s="43" t="n"/>
+      <c r="E58" s="43" t="n"/>
+      <c r="F58" s="43" t="n"/>
+      <c r="G58" s="43" t="n"/>
+      <c r="H58" s="43" t="n"/>
+      <c r="I58" s="43" t="n"/>
+      <c r="J58" s="43" t="n"/>
+      <c r="K58" s="43" t="n"/>
+      <c r="L58" s="43" t="n"/>
+      <c r="M58" s="43" t="n"/>
+      <c r="N58" s="43" t="n"/>
+      <c r="O58" s="43" t="n"/>
+      <c r="P58" s="43" t="n"/>
+      <c r="Q58" s="43" t="n"/>
+      <c r="R58" s="43" t="n"/>
+      <c r="S58" s="43" t="n"/>
+      <c r="T58" s="43" t="n"/>
+      <c r="U58" s="43" t="n"/>
+      <c r="V58" s="43" t="n"/>
+      <c r="W58" s="43" t="n"/>
+      <c r="X58" s="43" t="n"/>
+      <c r="Y58" s="43" t="n"/>
+      <c r="Z58" s="44" t="n"/>
+      <c r="AA58" s="37" t="n"/>
+      <c r="AB58" s="37" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="32" t="n"/>
+      <c r="B59" s="32" t="n"/>
+      <c r="C59" s="47" t="inlineStr">
+        <is>
+          <t>Superhost / Amato dagli ospiti  (badge top-left photo)</t>
+        </is>
+      </c>
+      <c r="AA59" s="37" t="n"/>
+      <c r="AB59" s="37" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="32" t="n"/>
+      <c r="B60" s="32" t="n"/>
+      <c r="C60" s="45" t="inlineStr">
+        <is>
+          <t>Appartamento · Milano  (title 22px bold)</t>
+        </is>
+      </c>
+      <c r="AA60" s="37" t="n"/>
+      <c r="AB60" s="37" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="32" t="n"/>
+      <c r="B61" s="32" t="n"/>
+      <c r="C61" s="46" t="inlineStr">
+        <is>
+          <t>Pellini 3 · 180mq · 4.93 (248)</t>
+        </is>
+      </c>
+      <c r="AA61" s="37" t="n"/>
+      <c r="AB61" s="37" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="32" t="n"/>
+      <c r="B62" s="48" t="n"/>
+      <c r="C62" s="49" t="inlineStr">
+        <is>
+          <t>983€ 532€ in totale  (prezzo strike+nuovo)</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="n"/>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="16" t="n"/>
+      <c r="G62" s="16" t="n"/>
+      <c r="H62" s="16" t="n"/>
+      <c r="I62" s="16" t="n"/>
+      <c r="J62" s="16" t="n"/>
+      <c r="K62" s="16" t="n"/>
+      <c r="L62" s="16" t="n"/>
+      <c r="M62" s="16" t="n"/>
+      <c r="N62" s="16" t="n"/>
+      <c r="O62" s="16" t="n"/>
+      <c r="P62" s="16" t="n"/>
+      <c r="Q62" s="16" t="n"/>
+      <c r="R62" s="16" t="n"/>
+      <c r="S62" s="16" t="n"/>
+      <c r="T62" s="16" t="n"/>
+      <c r="U62" s="16" t="n"/>
+      <c r="V62" s="16" t="n"/>
+      <c r="W62" s="16" t="n"/>
+      <c r="X62" s="16" t="n"/>
+      <c r="Y62" s="16" t="n"/>
+      <c r="Z62" s="16" t="n"/>
+      <c r="AA62" s="50" t="n"/>
+      <c r="AB62" s="37" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="32" t="n"/>
+      <c r="B63" s="53" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
+      <c r="E63" s="53" t="n"/>
+      <c r="F63" s="53" t="n"/>
+      <c r="G63" s="53" t="n"/>
+      <c r="H63" s="53" t="n"/>
+      <c r="I63" s="53" t="n"/>
+      <c r="J63" s="53" t="n"/>
+      <c r="K63" s="53" t="n"/>
+      <c r="L63" s="53" t="n"/>
+      <c r="M63" s="53" t="n"/>
+      <c r="N63" s="53" t="n"/>
+      <c r="O63" s="53" t="n"/>
+      <c r="P63" s="53" t="n"/>
+      <c r="Q63" s="53" t="n"/>
+      <c r="R63" s="53" t="n"/>
+      <c r="S63" s="53" t="n"/>
+      <c r="T63" s="53" t="n"/>
+      <c r="U63" s="53" t="n"/>
+      <c r="V63" s="53" t="n"/>
+      <c r="W63" s="53" t="n"/>
+      <c r="X63" s="53" t="n"/>
+      <c r="Y63" s="53" t="n"/>
+      <c r="Z63" s="53" t="n"/>
+      <c r="AA63" s="53" t="n"/>
+      <c r="AB63" s="37" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="32" t="n"/>
+      <c r="B64" s="53" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
+      <c r="E64" s="53" t="n"/>
+      <c r="F64" s="53" t="n"/>
+      <c r="G64" s="53" t="n"/>
+      <c r="H64" s="53" t="n"/>
+      <c r="I64" s="53" t="n"/>
+      <c r="J64" s="53" t="n"/>
+      <c r="K64" s="53" t="n"/>
+      <c r="L64" s="53" t="n"/>
+      <c r="M64" s="53" t="n"/>
+      <c r="N64" s="53" t="n"/>
+      <c r="O64" s="53" t="n"/>
+      <c r="P64" s="53" t="n"/>
+      <c r="Q64" s="53" t="n"/>
+      <c r="R64" s="53" t="n"/>
+      <c r="S64" s="53" t="n"/>
+      <c r="T64" s="53" t="n"/>
+      <c r="U64" s="53" t="n"/>
+      <c r="V64" s="53" t="n"/>
+      <c r="W64" s="53" t="n"/>
+      <c r="X64" s="53" t="n"/>
+      <c r="Y64" s="53" t="n"/>
+      <c r="Z64" s="53" t="n"/>
+      <c r="AA64" s="53" t="n"/>
+      <c r="AB64" s="37" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="32" t="n"/>
+      <c r="B65" s="53" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
+      <c r="E65" s="53" t="n"/>
+      <c r="F65" s="53" t="n"/>
+      <c r="G65" s="53" t="n"/>
+      <c r="H65" s="53" t="n"/>
+      <c r="I65" s="53" t="n"/>
+      <c r="J65" s="53" t="n"/>
+      <c r="K65" s="53" t="n"/>
+      <c r="L65" s="53" t="n"/>
+      <c r="M65" s="53" t="n"/>
+      <c r="N65" s="53" t="n"/>
+      <c r="O65" s="53" t="n"/>
+      <c r="P65" s="53" t="n"/>
+      <c r="Q65" s="53" t="n"/>
+      <c r="R65" s="53" t="n"/>
+      <c r="S65" s="53" t="n"/>
+      <c r="T65" s="53" t="n"/>
+      <c r="U65" s="53" t="n"/>
+      <c r="V65" s="53" t="n"/>
+      <c r="W65" s="53" t="n"/>
+      <c r="X65" s="53" t="n"/>
+      <c r="Y65" s="53" t="n"/>
+      <c r="Z65" s="53" t="n"/>
+      <c r="AA65" s="53" t="n"/>
+      <c r="AB65" s="37" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="32" t="n"/>
+      <c r="B66" s="53" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
+      <c r="E66" s="53" t="n"/>
+      <c r="F66" s="53" t="n"/>
+      <c r="G66" s="53" t="n"/>
+      <c r="H66" s="53" t="n"/>
+      <c r="I66" s="53" t="n"/>
+      <c r="J66" s="53" t="n"/>
+      <c r="K66" s="53" t="n"/>
+      <c r="L66" s="53" t="n"/>
+      <c r="M66" s="53" t="n"/>
+      <c r="N66" s="53" t="n"/>
+      <c r="O66" s="53" t="n"/>
+      <c r="P66" s="53" t="n"/>
+      <c r="Q66" s="53" t="n"/>
+      <c r="R66" s="53" t="n"/>
+      <c r="S66" s="53" t="n"/>
+      <c r="T66" s="53" t="n"/>
+      <c r="U66" s="53" t="n"/>
+      <c r="V66" s="53" t="n"/>
+      <c r="W66" s="53" t="n"/>
+      <c r="X66" s="53" t="n"/>
+      <c r="Y66" s="53" t="n"/>
+      <c r="Z66" s="53" t="n"/>
+      <c r="AA66" s="53" t="n"/>
+      <c r="AB66" s="37" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="48" t="n"/>
+      <c r="B67" s="54" t="n"/>
+      <c r="C67" s="54" t="n"/>
+      <c r="D67" s="54" t="n"/>
+      <c r="E67" s="54" t="n"/>
+      <c r="F67" s="54" t="n"/>
+      <c r="G67" s="54" t="n"/>
+      <c r="H67" s="54" t="n"/>
+      <c r="I67" s="54" t="n"/>
+      <c r="J67" s="54" t="n"/>
+      <c r="K67" s="54" t="n"/>
+      <c r="L67" s="54" t="n"/>
+      <c r="M67" s="54" t="n"/>
+      <c r="N67" s="54" t="n"/>
+      <c r="O67" s="54" t="n"/>
+      <c r="P67" s="54" t="n"/>
+      <c r="Q67" s="54" t="n"/>
+      <c r="R67" s="54" t="n"/>
+      <c r="S67" s="54" t="n"/>
+      <c r="T67" s="54" t="n"/>
+      <c r="U67" s="54" t="n"/>
+      <c r="V67" s="54" t="n"/>
+      <c r="W67" s="54" t="n"/>
+      <c r="X67" s="54" t="n"/>
+      <c r="Y67" s="54" t="n"/>
+      <c r="Z67" s="54" t="n"/>
+      <c r="AA67" s="54" t="n"/>
+      <c r="AB67" s="50" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1"/>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="68" t="inlineStr">
+        <is>
+          <t>◄── BOTTOM NAV (sticky position:fixed bottom · 5 voci icon+label) ──►</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="4" t="n"/>
+      <c r="R69" s="4" t="n"/>
+      <c r="S69" s="4" t="n"/>
+      <c r="T69" s="4" t="n"/>
+      <c r="U69" s="4" t="n"/>
+      <c r="V69" s="4" t="n"/>
+      <c r="W69" s="4" t="n"/>
+      <c r="X69" s="4" t="n"/>
+      <c r="Y69" s="4" t="n"/>
+      <c r="Z69" s="4" t="n"/>
+      <c r="AA69" s="4" t="n"/>
+      <c r="AB69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="32" t="n"/>
+      <c r="B70" s="53" t="n"/>
+      <c r="C70" s="53" t="n"/>
+      <c r="D70" s="53" t="n"/>
+      <c r="E70" s="53" t="n"/>
+      <c r="F70" s="53" t="n"/>
+      <c r="G70" s="53" t="n"/>
+      <c r="H70" s="53" t="n"/>
+      <c r="I70" s="53" t="n"/>
+      <c r="J70" s="53" t="n"/>
+      <c r="K70" s="53" t="n"/>
+      <c r="L70" s="53" t="n"/>
+      <c r="M70" s="53" t="n"/>
+      <c r="N70" s="53" t="n"/>
+      <c r="O70" s="53" t="n"/>
+      <c r="P70" s="53" t="n"/>
+      <c r="Q70" s="53" t="n"/>
+      <c r="R70" s="53" t="n"/>
+      <c r="S70" s="53" t="n"/>
+      <c r="T70" s="53" t="n"/>
+      <c r="U70" s="53" t="n"/>
+      <c r="V70" s="53" t="n"/>
+      <c r="W70" s="53" t="n"/>
+      <c r="X70" s="53" t="n"/>
+      <c r="Y70" s="53" t="n"/>
+      <c r="Z70" s="53" t="n"/>
+      <c r="AA70" s="53" t="n"/>
+      <c r="AB70" s="37" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="69" t="inlineStr">
+        <is>
+          <t>🔍
+Esplora
+(SEL)</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>♡
+Preferiti</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>🏠
+Viaggi</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="11" t="n"/>
+      <c r="R71" s="12" t="inlineStr">
+        <is>
+          <t>💬
+Messaggi
+•</t>
+        </is>
+      </c>
+      <c r="S71" s="4" t="n"/>
+      <c r="T71" s="4" t="n"/>
+      <c r="U71" s="4" t="n"/>
+      <c r="V71" s="11" t="n"/>
+      <c r="W71" s="12" t="inlineStr">
+        <is>
+          <t>👤
+Profilo</t>
+        </is>
+      </c>
+      <c r="X71" s="4" t="n"/>
+      <c r="Y71" s="4" t="n"/>
+      <c r="Z71" s="4" t="n"/>
+      <c r="AA71" s="4" t="n"/>
+      <c r="AB71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="15" t="n"/>
+      <c r="B72" s="16" t="n"/>
+      <c r="C72" s="16" t="n"/>
+      <c r="D72" s="16" t="n"/>
+      <c r="E72" s="17" t="n"/>
+      <c r="F72" s="15" t="n"/>
+      <c r="G72" s="16" t="n"/>
+      <c r="H72" s="16" t="n"/>
+      <c r="I72" s="16" t="n"/>
+      <c r="J72" s="16" t="n"/>
+      <c r="K72" s="17" t="n"/>
+      <c r="L72" s="15" t="n"/>
+      <c r="M72" s="16" t="n"/>
+      <c r="N72" s="16" t="n"/>
+      <c r="O72" s="16" t="n"/>
+      <c r="P72" s="16" t="n"/>
+      <c r="Q72" s="17" t="n"/>
+      <c r="R72" s="15" t="n"/>
+      <c r="S72" s="16" t="n"/>
+      <c r="T72" s="16" t="n"/>
+      <c r="U72" s="16" t="n"/>
+      <c r="V72" s="17" t="n"/>
+      <c r="W72" s="15" t="n"/>
+      <c r="X72" s="16" t="n"/>
+      <c r="Y72" s="16" t="n"/>
+      <c r="Z72" s="16" t="n"/>
+      <c r="AA72" s="16" t="n"/>
+      <c r="AB72" s="17" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="48" t="n"/>
+      <c r="B73" s="54" t="n"/>
+      <c r="C73" s="54" t="n"/>
+      <c r="D73" s="54" t="n"/>
+      <c r="E73" s="54" t="n"/>
+      <c r="F73" s="54" t="n"/>
+      <c r="G73" s="54" t="n"/>
+      <c r="H73" s="54" t="n"/>
+      <c r="I73" s="54" t="n"/>
+      <c r="J73" s="54" t="n"/>
+      <c r="K73" s="54" t="n"/>
+      <c r="L73" s="54" t="n"/>
+      <c r="M73" s="54" t="n"/>
+      <c r="N73" s="54" t="n"/>
+      <c r="O73" s="54" t="n"/>
+      <c r="P73" s="54" t="n"/>
+      <c r="Q73" s="54" t="n"/>
+      <c r="R73" s="54" t="n"/>
+      <c r="S73" s="54" t="n"/>
+      <c r="T73" s="54" t="n"/>
+      <c r="U73" s="54" t="n"/>
+      <c r="V73" s="54" t="n"/>
+      <c r="W73" s="54" t="n"/>
+      <c r="X73" s="54" t="n"/>
+      <c r="Y73" s="54" t="n"/>
+      <c r="Z73" s="54" t="n"/>
+      <c r="AA73" s="54" t="n"/>
+      <c r="AB73" s="50" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1"/>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>PATTERN UX MOBILE chiave:</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="55" t="inlineStr">
+        <is>
+          <t>• Map fullscreen-top + drawer pull-up (drag handle decorativo, drag verticale = expand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="55" t="inlineStr">
+        <is>
+          <t>• Header MAI mostra logo airbnb (solo la pillola contesto-corrente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="55" t="inlineStr">
+        <is>
+          <t>• Card 1 col, foto quasi quadrata, prezzo prominente (CTA conversion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="55" t="inlineStr">
+        <is>
+          <t>• Bottom nav sticky 5 voci (Esplora=current rosa #FF385C, altri grigi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="D3:Y5"/>
+    <mergeCell ref="A76:AB76"/>
+    <mergeCell ref="A32:AB32"/>
+    <mergeCell ref="A8:AB30"/>
+    <mergeCell ref="A35:AB35"/>
+    <mergeCell ref="R71:V72"/>
+    <mergeCell ref="C59:Z59"/>
+    <mergeCell ref="C60:Z60"/>
+    <mergeCell ref="B39:AA39"/>
+    <mergeCell ref="L31:Q31"/>
+    <mergeCell ref="L71:Q72"/>
+    <mergeCell ref="C61:Z61"/>
+    <mergeCell ref="A34:AB34"/>
+    <mergeCell ref="A77:AB77"/>
+    <mergeCell ref="A3:B5"/>
+    <mergeCell ref="A36:AB36"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="L48:Q48"/>
+    <mergeCell ref="A79:AB79"/>
+    <mergeCell ref="A6:AB6"/>
+    <mergeCell ref="A69:AB69"/>
+    <mergeCell ref="A78:AB78"/>
+    <mergeCell ref="AA3:AB5"/>
+    <mergeCell ref="C62:Z62"/>
+    <mergeCell ref="A75:AB75"/>
+    <mergeCell ref="F71:K72"/>
+    <mergeCell ref="W71:AB72"/>
+    <mergeCell ref="A71:E72"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb iPhone 14 Pro — tabella dimensioni misurate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Viewport 378×819 · DPR 1.25 · UA: Mozilla/5.0 (iPhone; CPU iPhone OS 18_5) · 24 card lazy-loaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t>Elemento</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>Selettore / aria-label</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>x px</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>y px</t>
+        </is>
+      </c>
+      <c r="E4" s="56" t="inlineStr">
+        <is>
+          <t>width px</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="inlineStr">
+        <is>
+          <t>height px</t>
+        </is>
+      </c>
+      <c r="G4" s="56" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="H4" s="56" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>viewport</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>window.innerWidth</t>
+        </is>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="59" t="n">
+        <v>378</v>
+      </c>
+      <c r="F5" s="59" t="n">
+        <v>819</v>
+      </c>
+      <c r="G5" s="58" t="inlineStr">
+        <is>
+          <t>browser</t>
+        </is>
+      </c>
+      <c r="H5" s="58" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro · DPR 1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>header pillola</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>button[aria-label="Milano: alloggi"]</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="D6" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="59" t="n">
+        <v>211</v>
+      </c>
+      <c r="F6" s="59" t="n">
+        <v>58</v>
+      </c>
+      <c r="G6" s="58" t="inlineStr">
+        <is>
+          <t>viewport</t>
+        </is>
+      </c>
+      <c r="H6" s="58" t="inlineStr">
+        <is>
+          <t>pillola compatta · click → modale searchbar fullscreen accordion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  back icon</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>button[aria-label="Indietro"]</t>
+        </is>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+      <c r="H7" s="58" t="inlineStr">
+        <is>
+          <t>top-left · ← ritorna a home</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  filtri icon</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>button[aria-label="Mostra i filtri"]</t>
+        </is>
+      </c>
+      <c r="C8" s="59" t="n">
+        <v>299</v>
+      </c>
+      <c r="D8" s="59" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+      <c r="H8" s="58" t="inlineStr">
+        <is>
+          <t>top-right · ≡ → modale Filtri fullscreen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>[data-testid="map/GoogleMap"]</t>
+        </is>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="59" t="n">
+        <v>363</v>
+      </c>
+      <c r="F9" s="59" t="n">
+        <v>788</v>
+      </c>
+      <c r="G9" s="58" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="H9" s="58" t="inlineStr">
+        <is>
+          <t>fullscreen TOP · 24 marker prezzo · click marker = scroll card</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>drag handle</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>(div h≈4 centrata)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="n">
+        <v>103</v>
+      </c>
+      <c r="D10" s="59" t="n">
+        <v>500</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>157</v>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="58" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="H10" s="58" t="inlineStr">
+        <is>
+          <t>pill grigia · drag verticale = espande/riduce drawer (pattern bottom-sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>drawer (default)</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>(parent del card list)</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>515</v>
+      </c>
+      <c r="E11" s="59" t="n">
+        <v>378</v>
+      </c>
+      <c r="F11" s="59" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="H11" s="58" t="inlineStr">
+        <is>
+          <t>pull-up · peek-bottom default · contiene heading + sort + lista cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  heading</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>h1 "Oltre 1.000 alloggi"</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <v>580</v>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>378</v>
+      </c>
+      <c r="F12" s="59" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" s="58" t="inlineStr">
+        <is>
+          <t>drawer</t>
+        </is>
+      </c>
+      <c r="H12" s="58" t="inlineStr">
+        <is>
+          <t>centrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  sort label</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>"Come ordiniamo i risultati"</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>605</v>
+      </c>
+      <c r="E13" s="59" t="n">
+        <v>378</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>18</v>
+      </c>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>drawer</t>
+        </is>
+      </c>
+      <c r="H13" s="58" t="inlineStr">
+        <is>
+          <t>link con info icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  card #1</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>[itemprop="itemListElement"]</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <v>515</v>
+      </c>
+      <c r="E14" s="59" t="n">
+        <v>315</v>
+      </c>
+      <c r="F14" s="59" t="n">
+        <v>451</v>
+      </c>
+      <c r="G14" s="58" t="inlineStr">
+        <is>
+          <t>drawer</t>
+        </is>
+      </c>
+      <c r="H14" s="58" t="inlineStr">
+        <is>
+          <t>1 per riga · foto + meta + prezzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    photo</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>img</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>515</v>
+      </c>
+      <c r="E15" s="59" t="n">
+        <v>315</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>395</v>
+      </c>
+      <c r="G15" s="58" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="H15" s="58" t="inlineStr">
+        <is>
+          <t>aspect 0.80 (315/395) · object-fit cover · radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    superhost badge</t>
+        </is>
+      </c>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>(span overlay top-left)</t>
+        </is>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <v>530</v>
+      </c>
+      <c r="E16" s="59" t="n">
+        <v>90</v>
+      </c>
+      <c r="F16" s="59" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="58" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="H16" s="58" t="inlineStr">
+        <is>
+          <t>optional · "Superhost" / "Amato dagli ospiti" / vuoto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    heart btn</t>
+        </is>
+      </c>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>button (top-right photo)</t>
+        </is>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>287</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>525</v>
+      </c>
+      <c r="E17" s="59" t="n">
+        <v>32</v>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>32</v>
+      </c>
+      <c r="G17" s="58" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="H17" s="58" t="inlineStr">
+        <is>
+          <t>♡ salva preferiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    title</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>"Appartamento · Milano"</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>920</v>
+      </c>
+      <c r="E18" s="59" t="n">
+        <v>315</v>
+      </c>
+      <c r="F18" s="59" t="n">
+        <v>22</v>
+      </c>
+      <c r="G18" s="58" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="H18" s="58" t="inlineStr">
+        <is>
+          <t>h2 22px / 700</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    meta</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>"Pellini 3 · 180mq · ★4.93 (248)"</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>942</v>
+      </c>
+      <c r="E19" s="59" t="n">
+        <v>315</v>
+      </c>
+      <c r="F19" s="59" t="n">
+        <v>18</v>
+      </c>
+      <c r="G19" s="58" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="H19" s="58" t="inlineStr">
+        <is>
+          <t>rating + meta su singola riga (compatto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    price</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>"983€ 532€ in totale"</t>
+        </is>
+      </c>
+      <c r="C20" s="59" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" s="59" t="n">
+        <v>962</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>315</v>
+      </c>
+      <c r="F20" s="59" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" s="58" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="H20" s="58" t="inlineStr">
+        <is>
+          <t>strike + nuovo · bold</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="57" t="inlineStr">
+        <is>
+          <t>bottom nav</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>(div fixed bottom 5 voci)</t>
+        </is>
+      </c>
+      <c r="C21" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <v>771</v>
+      </c>
+      <c r="E21" s="59" t="n">
+        <v>378</v>
+      </c>
+      <c r="F21" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G21" s="58" t="inlineStr">
+        <is>
+          <t>viewport</t>
+        </is>
+      </c>
+      <c r="H21" s="58" t="inlineStr">
+        <is>
+          <t>STICKY · 5 voci icon+label</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Esplora (current)</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>(rosa #FF385C)</t>
+        </is>
+      </c>
+      <c r="C22" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="59" t="n">
+        <v>771</v>
+      </c>
+      <c r="E22" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="F22" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G22" s="58" t="inlineStr">
+        <is>
+          <t>bottom-nav</t>
+        </is>
+      </c>
+      <c r="H22" s="58" t="inlineStr">
+        <is>
+          <t>🔍 + label · current state</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Preferiti</t>
+        </is>
+      </c>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>(grigio default)</t>
+        </is>
+      </c>
+      <c r="C23" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="D23" s="59" t="n">
+        <v>771</v>
+      </c>
+      <c r="E23" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="F23" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G23" s="58" t="inlineStr">
+        <is>
+          <t>bottom-nav</t>
+        </is>
+      </c>
+      <c r="H23" s="58" t="inlineStr">
+        <is>
+          <t>♡ + label</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Viaggi</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>(grigio default)</t>
+        </is>
+      </c>
+      <c r="C24" s="59" t="n">
+        <v>152</v>
+      </c>
+      <c r="D24" s="59" t="n">
+        <v>771</v>
+      </c>
+      <c r="E24" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="F24" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G24" s="58" t="inlineStr">
+        <is>
+          <t>bottom-nav</t>
+        </is>
+      </c>
+      <c r="H24" s="58" t="inlineStr">
+        <is>
+          <t>🏠 logo airbnb mini + label</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Messaggi</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>(grigio + dot rosso)</t>
+        </is>
+      </c>
+      <c r="C25" s="59" t="n">
+        <v>228</v>
+      </c>
+      <c r="D25" s="59" t="n">
+        <v>771</v>
+      </c>
+      <c r="E25" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="F25" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G25" s="58" t="inlineStr">
+        <is>
+          <t>bottom-nav</t>
+        </is>
+      </c>
+      <c r="H25" s="58" t="inlineStr">
+        <is>
+          <t>💬 + label · badge unread (•)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Profilo</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>(grigio default)</t>
+        </is>
+      </c>
+      <c r="C26" s="59" t="n">
+        <v>304</v>
+      </c>
+      <c r="D26" s="59" t="n">
+        <v>771</v>
+      </c>
+      <c r="E26" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="F26" s="59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G26" s="58" t="inlineStr">
+        <is>
+          <t>bottom-nav</t>
+        </is>
+      </c>
+      <c r="H26" s="58" t="inlineStr">
+        <is>
+          <t>👤 + label</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Airbnb iPhone — Flow searchbar accordion + Filtri fullscreen + drag handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>SEARCHBAR MOBILE — Modale fullscreen ACCORDION (3 step progressive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="55" t="inlineStr">
+        <is>
+          <t>Trigger: tap sulla pillola searchbar nel header. Apre modale fullscreen 378×819 con tabs 🏠Alloggi / 🎈Esperienze / 🛎️Servizi in alto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>Contenuto</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>Footer / CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="71" t="inlineStr">
+        <is>
+          <t>1️⃣ Dove? (espansa di default)</t>
+        </is>
+      </c>
+      <c r="B7" s="72" t="inlineStr">
+        <is>
+          <t>Search input "Milano" + Lista "Ricerche recenti" (Milano · 18-24 mag, Scauri · 11-18 mag) + "Destinazioni suggerite" (📍Nelle vicinanze, 🏙️Milano Lombardia "Ideale per famiglie", 🇫🇷Parigi…)</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="inlineStr">
+        <is>
+          <t>Footer: "Cancella tutto" sx + 🔍 "Ricerca" rosa CTA dx (oppure tap "Quando" collapsed sotto per andare avanti)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="71" t="inlineStr">
+        <is>
+          <t>2️⃣ Quando?</t>
+        </is>
+      </c>
+      <c r="B8" s="72" t="inlineStr">
+        <is>
+          <t>Toggle segmented "Date | Date flessibili" + Calendar 1 mese alla volta (vs 2 mesi affiancati desktop) + "Carica date precedenti" btn + Footer dropdowns "Check-in/Check-out: Giorno esatto" (precision flexibility)</t>
+        </is>
+      </c>
+      <c r="C8" s="72" t="inlineStr">
+        <is>
+          <t>Footer: "Ripristina" sx + "Avanti" CTA NERO dx (step-progression, NO Ricerca qui)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="71" t="inlineStr">
+        <is>
+          <t>3️⃣ Chi?</t>
+        </is>
+      </c>
+      <c r="B9" s="72" t="inlineStr">
+        <is>
+          <t>Stepper ± per 4 categorie: Adulti (Da 13 in su) · Bambini (Da 2 a 12 anni) · Neonati (Fino a 2 anni) · Animali domestici (link "Viaggi con un animale di servizio?")</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
+        <is>
+          <t>Footer: "Cancella tutto" sx + 🔍 "Ricerca" rosa CTA dx (CTA finale, lancia la ricerca)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="71" t="inlineStr">
+        <is>
+          <t>🔄 Backtracking</t>
+        </is>
+      </c>
+      <c r="B10" s="72" t="inlineStr">
+        <is>
+          <t>Sezioni precedenti restano visibili come collapsed cards in cima (mostrano "Dove · Milano, Lombardia" / "Quando · 18 mag - 24 mag"). Tap su una di esse riapre quella sezione.</t>
+        </is>
+      </c>
+      <c r="C10" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="71" t="inlineStr">
+        <is>
+          <t>❌ Chiudi</t>
+        </is>
+      </c>
+      <c r="B11" s="72" t="inlineStr">
+        <is>
+          <t>Top-right: bottone X tondo per chiudere modale senza applicare modifiche. Comportamento: torna a pagina lista cards.</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>FILTRI MOBILE — Modale fullscreen (NON bottom-sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>Trigger: tap icona ≡ filtri (top-right header). Modale fullscreen 378×~auto (scroll interno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>Sezione</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>Pattern UI</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>Note vs desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>Titolo "Filtri" centrato + ✕ chiudi top-right</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="57" t="inlineStr">
+        <is>
+          <t>1. Consigliati per te</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>3 tile-card (vs 4 desktop): icone illustrate (2+ camere · Culla · Lavatrice)</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>Adapt per mobile width</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>2. Tipo di alloggio</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>Segmented 3 (Qualsiasi tipo / Stanza / Casa intera)</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="57" t="inlineStr">
+        <is>
+          <t>3. Fascia di prezzo</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>Slider min/max + HISTOGRAM signature pattern + 2 input "€50" / "€2600+"</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop · scrollable se largo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="57" t="inlineStr">
+        <is>
+          <t>4. Stanze e letti</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>Stepper ± per Camere / Letti / Bagni</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>5. Servizi</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>Checkbox grid (WiFi / AC / Cucina / Lavatrice...) con "Mostra di più"</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="57" t="inlineStr">
+        <is>
+          <t>6. Opzioni di prenotazione</t>
+        </is>
+      </c>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>4 chip toggle (Prenotazione immediata / Self check-in / Cancellazione gratuita / Animali ammessi)</t>
+        </is>
+      </c>
+      <c r="C23" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="57" t="inlineStr">
+        <is>
+          <t>7. Alloggi straordinari</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>2 tile (Amato dagli ospiti / Luxe)</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="57" t="inlineStr">
+        <is>
+          <t>8-10. Tipo accordion / Accessibilità / Lingua</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>Accordion ▼ collapsed default</t>
+        </is>
+      </c>
+      <c r="C25" s="58" t="inlineStr">
+        <is>
+          <t>Identico desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>Footer fisso</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>"Cancella tutto" sx + "Mostra oltre 1.000 alloggi" CTA NERO #222222 dx (LIVE COUNT update ogni filtro)</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>⚠️ CTA NERO mobile vs ROSA #FF385C desktop! Pattern intenzionale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="74" t="inlineStr">
+        <is>
+          <t>DRAG HANDLE — Map ↔ Drawer toggle (pattern bottom-sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>Linea grigia centrata orizzontalmente · 157×0px coordinate (visualmente pill 30×4) · sotto la mappa, sopra al drawer</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="57" t="inlineStr">
+        <is>
+          <t>Stato 1: Drawer chiuso (default)</t>
+        </is>
+      </c>
+      <c r="B31" s="58" t="inlineStr">
+        <is>
+          <t>Map fullscreen-top 363×788 · drawer peek-bottom (mostra h1 "Oltre 1.000 alloggi" + prima card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="57" t="inlineStr">
+        <is>
+          <t>Stato 2: Drawer aperto (drag-up)</t>
+        </is>
+      </c>
+      <c r="B32" s="58" t="inlineStr">
+        <is>
+          <t>Map collassa a peek-top · drawer espanso fullscreen mostra lista cards (1-col)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="57" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="B33" s="58" t="inlineStr">
+        <is>
+          <t>Drag verticale sul handle (touch swipe up/down) — NO tap-toggle (handle è decorativo, non button)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="57" t="inlineStr">
+        <is>
+          <t>URL state</t>
+        </is>
+      </c>
+      <c r="B34" s="58" t="inlineStr">
+        <is>
+          <t>drawer_open=true|false in querystring · permette deep-link in stato esplicito</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="57" t="inlineStr">
+        <is>
+          <t>UX rationale</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="inlineStr">
+        <is>
+          <t>L'utente sceglie quanto della mappa vs lista vedere. Default: mappa per esplorazione geografica, drawer drag per leggere lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="75" t="inlineStr">
+        <is>
+          <t>IMPLICAZIONI per redesign LivingApple wizardstep1:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="76" t="inlineStr">
+        <is>
+          <t>1. La pillola searchbar mobile è UN SOLO touch target (vs 3 segmenti desktop) → in LivingApple già funziona (HomeSearch è bottone unico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t>2. La modale searchbar è ACCORDION step-by-step (Dove → Quando → Chi) → in LivingApple wizardstep1 ha già una flow simile (residenza → date → ospiti → offerta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="76" t="inlineStr">
+        <is>
+          <t>3. La separazione Searchbar (modificare ricerca) vs Filtri (raffinare) è netta in Airbnb → utile mantenere in LivingApple: chip-bar above-fold per filtri rapidi + modale Filtri completa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="76" t="inlineStr">
+        <is>
+          <t>4. CTA mobile NERO vs ROSA desktop → LivingApple potrebbe usare pattern simile (grigio scuro su mobile per non saturare, brand color su desktop dove c'è più white-space).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="76" t="inlineStr">
+        <is>
+          <t>5. LIVE COUNT footer "Mostra oltre 1.000 alloggi" → LivingApple non ha questo, da introdurre nei filtri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="76" t="inlineStr">
+        <is>
+          <t>6. Drag handle map↔list → NON applicabile a LivingApple (non abbiamo mappa, non è il nostro fulcro UX).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="76" t="inlineStr">
+        <is>
+          <t>7. Bottom nav 5 voci → NON applicabile a LivingApple (non è una platform multipage tipo airbnb/booking).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>